--- a/public/alumni-data.xlsx
+++ b/public/alumni-data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N341"/>
+  <dimension ref="A1:N340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11385,12 +11385,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ronica Cheng</t>
+          <t>Maryam Mussa</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Alpha Xi</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11401,22 +11401,22 @@
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ronica-cheng/</t>
+          <t>https://www.linkedin.com/in/maryammussa/</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Associate Product Marketing Manager</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -11429,7 +11429,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Maryam Mussa</t>
+          <t>Jacob Won</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11445,22 +11445,22 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Stack Fulfillment</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/maryammussa/</t>
+          <t>https://www.linkedin.com/in/jacobwon/</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Associate Product Marketing Manager</t>
+          <t>Director of Operations</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -11473,40 +11473,32 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Jacob Won</t>
+          <t>Alec Wong</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Alpha Xi</t>
+          <t>Alpha Beta</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Lough-Yu</t>
+          <t>Chang-McGrath</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Stack Fulfillment</t>
-        </is>
-      </c>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jacobwon/</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Director of Operations</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/in/alecwong44/</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
@@ -11517,12 +11509,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Alec Wong</t>
+          <t>Ashley Yeh</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Alpha Beta</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11533,16 +11525,24 @@
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Flexspeak</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alecwong44/</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>https://www.linkedin.com/in/ashley-yeh/</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
@@ -11553,12 +11553,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ashley Yeh</t>
+          <t>Kelsie Kim</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11569,22 +11569,22 @@
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Flexspeak</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ashley-yeh/</t>
+          <t>https://www.linkedin.com/in/kelsiejkim/</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Product Marketer</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -11597,12 +11597,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Kelsie Kim</t>
+          <t>Julitza Alvarez</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Omicron</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11618,17 +11618,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>California Democratic Party</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kelsiejkim/</t>
+          <t>https://www.linkedin.com/in/julitzaalvarez/</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Product Marketer</t>
+          <t>Delegate</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -11641,12 +11641,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Julitza Alvarez</t>
+          <t>Ryan Eshaghi</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Alpha Omicron</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11657,22 +11657,22 @@
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>California Democratic Party</t>
+          <t>Forethought</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/julitzaalvarez/</t>
+          <t>https://www.linkedin.com/in/ryaneshaghi/</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Delegate</t>
+          <t>Manager, Customer Success</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -11685,12 +11685,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Ryan Eshaghi</t>
+          <t>Julie Le Trinh</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11701,22 +11701,22 @@
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Forethought</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ryaneshaghi/</t>
+          <t>https://www.linkedin.com/in/julieletrinh/</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Manager, Customer Success</t>
+          <t>Senior Associate</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -11729,12 +11729,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Julie Le Trinh</t>
+          <t>Kelly Cheng</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11745,22 +11745,22 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Media/Entertainment</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Olaplex Inc. (Nasdaq: OLPX)</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/julieletrinh/</t>
+          <t>https://www.linkedin.com/in/kellychengg/</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Senior Associate</t>
+          <t>Senior Social Media Associate</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -11773,12 +11773,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Kelly Cheng</t>
+          <t>Grace Hsiang</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11789,22 +11789,22 @@
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Media/Entertainment</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Olaplex Inc. (Nasdaq: OLPX)</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kellychengg/</t>
+          <t>https://www.linkedin.com/in/grace-hsiang/</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Senior Social Media Associate</t>
+          <t>Client Solutions Manager</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -11817,12 +11817,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Grace Hsiang</t>
+          <t xml:space="preserve">Jenny Wu </t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11833,22 +11833,22 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/grace-hsiang/</t>
+          <t>https://www.linkedin.com/in/jennyywuu/</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Client Solutions Manager</t>
+          <t>Compensation Analyst</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -11861,12 +11861,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jenny Wu </t>
+          <t>Jana Zweigoron</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Beta</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11877,22 +11877,22 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jennyywuu/</t>
+          <t>https://www.linkedin.com/in/janazweigoron/</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Compensation Analyst</t>
+          <t>Splunk Platform Partner Go-To-Market Manager</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -11905,12 +11905,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Jana Zweigoron</t>
+          <t>Aryan Ghanadan</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Alpha Beta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/janazweigoron/</t>
+          <t>https://www.linkedin.com/in/aryan-ghanadan/</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Splunk Platform Partner Go-To-Market Manager</t>
+          <t>Guest Experiences Lead</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -11949,12 +11949,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Aryan Ghanadan</t>
+          <t>Kevin Cao</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11965,22 +11965,22 @@
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Golden State Warriors</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aryan-ghanadan/</t>
+          <t>https://www.linkedin.com/in/kevinkwcao/</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Guest Experiences Lead</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -11993,40 +11993,28 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Kevin Cao</t>
+          <t>Brandon Liu</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Theta</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chang-McGrath</t>
+          <t>Chen-Ho</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Project Management</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/kevinkwcao/</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
@@ -12037,12 +12025,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Brandon Liu</t>
+          <t>Lia Ikeda</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Theta</t>
+          <t>Alpha Beta</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -12053,12 +12041,24 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lia-ikeda/</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Strategic Partnerships Manager</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
@@ -12069,12 +12069,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Lia Ikeda</t>
+          <t>Aimee Han</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Alpha Beta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -12085,22 +12085,22 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Workstream</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lia-ikeda/</t>
+          <t>https://www.linkedin.com/in/aimeeyh/</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Strategic Partnerships Manager</t>
+          <t>Strategic Finance &amp; Analytics</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -12113,12 +12113,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Aimee Han</t>
+          <t>Tiffany Than</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -12129,22 +12129,22 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aimeeyh/</t>
+          <t>https://www.linkedin.com/in/tiffany-than/</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Strategic Finance &amp; Analytics</t>
+          <t>Workforce Analyst</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -12157,12 +12157,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Tiffany Than</t>
+          <t>Darren Han</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -12178,17 +12178,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tiffany-than/</t>
+          <t>https://www.linkedin.com/in/darrenhan/</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Workforce Analyst</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -12201,12 +12201,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Darren Han</t>
+          <t>Michael Duan</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -12217,22 +12217,22 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/darrenhan/</t>
+          <t>https://www.linkedin.com/in/michaelranduan/</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -12245,12 +12245,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Michael Duan</t>
+          <t>Cody Enokida</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/michaelranduan/</t>
+          <t>https://www.linkedin.com/in/codyenokida/</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -12289,12 +12289,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Cody Enokida</t>
+          <t>Brennen Wong</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/codyenokida/</t>
+          <t>https://www.linkedin.com/in/brennenwong/</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -12333,12 +12333,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Brennen Wong</t>
+          <t>Henry Wang</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -12349,22 +12349,22 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/brennenwong/</t>
+          <t>https://www.linkedin.com/in/henrykw/</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Strategy &amp; Analytics Lead</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -12377,12 +12377,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Henry Wang</t>
+          <t>Alex Pham</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -12393,22 +12393,22 @@
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/henrykw/</t>
+          <t>https://www.linkedin.com/in/alexatp/</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Strategy &amp; Analytics Lead</t>
+          <t>Business Analyst 2</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -12421,12 +12421,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Alex Pham</t>
+          <t>Emily Ros</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12437,22 +12437,22 @@
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>EdgeTrace</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alexatp/</t>
+          <t>https://www.linkedin.com/in/emilyros117/</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Business Analyst 2</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -12465,12 +12465,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Emily Ros</t>
+          <t>Jin Fukusumi</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12481,24 +12481,16 @@
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>EdgeTrace</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/emilyros117/</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Marketing Manager</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/in/jinfukusumi/</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
@@ -12509,12 +12501,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Jin Fukusumi</t>
+          <t>Lavanya Bhalla</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12525,16 +12517,24 @@
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr"/>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jinfukusumi/</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr"/>
+          <t>https://www.linkedin.com/in/lavanyabhalla/</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>CSG - Strategy &amp; Analytics Senior Analyst</t>
+        </is>
+      </c>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
@@ -12545,12 +12545,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Lavanya Bhalla</t>
+          <t>Chuck Wong</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12561,24 +12561,12 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/lavanyabhalla/</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>CSG - Strategy &amp; Analytics Senior Analyst</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
@@ -12589,12 +12577,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Chuck Wong</t>
+          <t>Neil Wong</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -12605,12 +12593,24 @@
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neilkenwong/</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
@@ -12621,12 +12621,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Neil Wong</t>
+          <t>Patrick Tu</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -12637,22 +12637,22 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Commure</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/neilkenwong/</t>
+          <t>https://www.linkedin.com/in/patrickltu/</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Corporate Strategy &amp; Development - Strategic Partnerships</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -12665,38 +12665,38 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Patrick Tu</t>
+          <t>Daanya Anand</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Chen-Ho</t>
+          <t>Chew-Mark</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Commure</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/patrickltu/</t>
+          <t>https://www.linkedin.com/in/daanyaanand/</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Corporate Strategy &amp; Development - Strategic Partnerships</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -12709,12 +12709,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Daanya Anand</t>
+          <t>Derek Chang</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12730,17 +12730,17 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/daanyaanand/</t>
+          <t>https://www.linkedin.com/in/derektchang/</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -12753,12 +12753,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Derek Chang</t>
+          <t>Sean Devine</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12774,12 +12774,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/derektchang/</t>
+          <t>https://www.linkedin.com/in/devine-sean/</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -12797,12 +12797,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sean Devine</t>
+          <t>Lynn Phan</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12813,22 +12813,22 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UCSF Health</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/devine-sean/</t>
+          <t>https://www.linkedin.com/in/lynnphanrn/</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Clinical Nurse II</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -12841,12 +12841,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Lynn Phan</t>
+          <t>Uyen Sy</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12857,22 +12857,22 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>UCSF Health</t>
+          <t>Day One Biopharmaceuticals</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lynnphanrn/</t>
+          <t>https://www.linkedin.com/in/uyensy/</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Clinical Nurse II</t>
+          <t>Accounting Manager</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -12885,12 +12885,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Uyen Sy</t>
+          <t>Julie Luu</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12901,22 +12901,22 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Day One Biopharmaceuticals</t>
+          <t>Anaplan</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/uyensy/</t>
+          <t>https://www.linkedin.com/in/julie-luu64/</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Accounting Manager</t>
+          <t>Account-Based Marketing Specialist</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -12929,12 +12929,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Julie Luu</t>
+          <t xml:space="preserve">Sumin Sung </t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Xi</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12945,22 +12945,22 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Anaplan</t>
+          <t>Hawaii Foodservice Alliance LLC</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/julie-luu64/</t>
+          <t>https://www.linkedin.com/in/suminsung/</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Account-Based Marketing Specialist</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -12973,38 +12973,38 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sumin Sung </t>
+          <t>Alec Lau</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Alpha Xi</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chew-Mark</t>
+          <t>Huang-Merchant</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Hawaii Foodservice Alliance LLC</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/suminsung/</t>
+          <t>https://www.linkedin.com/in/laualec/</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Senior Analyst, Development Finance</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -13017,12 +13017,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Alec Lau</t>
+          <t>Deborah Yeung</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -13038,17 +13038,17 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/laualec/</t>
+          <t>https://www.linkedin.com/in/deborahhyeung/</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Senior Analyst, Development Finance</t>
+          <t>Corporate Finance &amp; Strategy Senior Associate</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -13061,12 +13061,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Deborah Yeung</t>
+          <t>Mohit Shah</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -13077,22 +13077,22 @@
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/deborahhyeung/</t>
+          <t>https://www.linkedin.com/in/mohitmshah/</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Corporate Finance &amp; Strategy Senior Associate</t>
+          <t>Associate Manager, Monetization Strategy</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -13105,12 +13105,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Mohit Shah</t>
+          <t>Suman Gujju</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Mu</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -13121,22 +13121,22 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Product Management</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohitmshah/</t>
+          <t>https://www.linkedin.com/in/suman-gujju/</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Associate Manager, Monetization Strategy</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -13149,12 +13149,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Suman Gujju</t>
+          <t>Farbod Rafezy</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Alpha Mu</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13165,22 +13165,22 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/suman-gujju/</t>
+          <t>https://www.linkedin.com/in/frafezy/</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -13193,12 +13193,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Farbod Rafezy</t>
+          <t>Grace Till</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -13209,22 +13209,22 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>American Securities</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/frafezy/</t>
+          <t>https://www.linkedin.com/in/gracetill/</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Investor Relations Associate</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -13237,12 +13237,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Grace Till</t>
+          <t>Isaiah Abeyta</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -13253,22 +13253,22 @@
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>American Securities</t>
+          <t>Crowell &amp; Moring</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gracetill/</t>
+          <t>https://www.linkedin.com/in/isaiahabeyta/</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Investor Relations Associate</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -13281,12 +13281,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Isaiah Abeyta</t>
+          <t>Kristen Chan</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13297,22 +13297,22 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Crowell &amp; Moring</t>
+          <t>Qualtrics</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/isaiahabeyta/</t>
+          <t>https://www.linkedin.com/in/kristhc/</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Global Benefits Analyst</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -13325,12 +13325,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Kristen Chan</t>
+          <t>Brandon Khong</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -13341,22 +13341,22 @@
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Qualtrics</t>
+          <t xml:space="preserve">Impulse Space </t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kristhc/</t>
+          <t>https://www.linkedin.com/in/brandonkhong/</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Global Benefits Analyst</t>
+          <t>Flight Software Engineer</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -13369,12 +13369,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Brandon Khong</t>
+          <t>Sangmin Oh</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -13385,24 +13385,12 @@
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Impulse Space </t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/brandonkhong/</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Flight Software Engineer</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
@@ -13413,7 +13401,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Sangmin Oh</t>
+          <t>Martin Leung</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13429,12 +13417,24 @@
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>climbing cat</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-leung/</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Builder</t>
+        </is>
+      </c>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
@@ -13445,12 +13445,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Martin Leung</t>
+          <t>Melanie Huang</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -13461,22 +13461,22 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>climbing cat</t>
+          <t>Princess Polly</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/martin-leung/</t>
+          <t>https://www.linkedin.com/in/melanie-huang/</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Builder</t>
+          <t>UX E-Commerce Manager</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -13489,12 +13489,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Melanie Huang</t>
+          <t>Maxwell Xu</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -13505,22 +13505,22 @@
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Princess Polly</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/melanie-huang/</t>
+          <t>https://www.linkedin.com/in/maxwellxu/</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>UX E-Commerce Manager</t>
+          <t>Product Marketing Manager</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -13533,12 +13533,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Maxwell Xu</t>
+          <t>Gracie Wong</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Gamma</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -13549,22 +13549,22 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alinea Invest</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/maxwellxu/</t>
+          <t>https://www.linkedin.com/in/graciezwang/</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Product Marketing Manager</t>
+          <t>Growth Marketing Manager</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -13577,12 +13577,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Gracie Wong</t>
+          <t>Eugene Jeon</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Alpha Gamma</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13593,22 +13593,22 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Alinea Invest</t>
+          <t>Capital Group</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/graciezwang/</t>
+          <t>https://www.linkedin.com/in/eugenemjeon/</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Growth Marketing Manager</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -13621,12 +13621,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Eugene Jeon</t>
+          <t>Travis Abshire</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13637,22 +13637,22 @@
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>Silicon Beach Solutions, LLC.</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/eugenemjeon/</t>
+          <t>https://www.linkedin.com/in/travisjabshire/</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Senior Project Manager</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -13665,12 +13665,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Travis Abshire</t>
+          <t>Jason Cao</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13681,22 +13681,22 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Silicon Beach Solutions, LLC.</t>
+          <t>J.P. Morgan</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/travisjabshire/</t>
+          <t>https://www.linkedin.com/in/jasontcao/</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Senior Project Manager</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -13709,12 +13709,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Jason Cao</t>
+          <t>Nicholas Wong</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13725,22 +13725,22 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
+          <t>Inari Medical</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jasontcao/</t>
+          <t>https://www.linkedin.com/in/nwong2120/</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Financial Analyst, LimFlow BU</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -13753,12 +13753,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Nicholas Wong</t>
+          <t>Mark Membrebe</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13769,24 +13769,16 @@
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Inari Medical</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/nwong2120/</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>Financial Analyst, LimFlow BU</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/in/markmembrebe1/</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
@@ -13797,12 +13789,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Mark Membrebe</t>
+          <t>Albert Tang</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Delta</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13813,16 +13805,24 @@
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr"/>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Albertsons Companies</t>
+        </is>
+      </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/markmembrebe1/</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr"/>
+          <t>https://www.linkedin.com/in/albertwtang/</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Manager, Personalization </t>
+        </is>
+      </c>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
@@ -13833,12 +13833,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Albert Tang</t>
+          <t>Gaurav Mohan</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Alpha Delta</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13849,22 +13849,22 @@
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Albertsons Companies</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/albertwtang/</t>
+          <t>https://www.linkedin.com/in/gaurav-mohan/</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Product Manager, Personalization </t>
+          <t>Data Scientist, Full Stack</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -13877,38 +13877,38 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gaurav Mohan</t>
+          <t>Jonas Xie</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Huang-Merchant</t>
+          <t>Liang-Lin</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gaurav-mohan/</t>
+          <t>https://www.linkedin.com/in/jonasxie/</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Data Scientist, Full Stack</t>
+          <t>Sr. Investment Performance Analyst</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -13921,12 +13921,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Jonas Xie</t>
+          <t>Ryan To</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13937,22 +13937,22 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Founders, Inc.</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jonasxie/</t>
+          <t>https://www.linkedin.com/in/ryanto01/</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Sr. Investment Performance Analyst</t>
+          <t>Founder in Residence</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -13965,12 +13965,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ryan To</t>
+          <t>Marissa Koo</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Gamma</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13981,22 +13981,22 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Founders, Inc.</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ryanto01/</t>
+          <t>https://www.linkedin.com/in/marissakoo/</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Founder in Residence</t>
+          <t>Campaign Manager</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -14009,12 +14009,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Marissa Koo</t>
+          <t>Jocelyn Kuo</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Alpha Gamma</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -14025,22 +14025,22 @@
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/marissakoo/</t>
+          <t>https://www.linkedin.com/in/jocelyn-kuo/</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Campaign Manager</t>
+          <t>Emerging Talent Program Manager</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -14053,12 +14053,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Jocelyn Kuo</t>
+          <t>Yeseo Han</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -14069,22 +14069,22 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>SoKit Beauty</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jocelyn-kuo/</t>
+          <t>https://www.linkedin.com/in/yeseo-han/</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Emerging Talent Program Manager</t>
+          <t>Digital Marketing &amp; Sales Strategy Intern</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
@@ -14097,17 +14097,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Yeseo Han</t>
+          <t>Kenny Pham</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Beta</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Liang-Lin</t>
+          <t>Su-Hung-Green</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -14118,17 +14118,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SoKit Beauty</t>
+          <t>NZXT, Inc.</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/yeseo-han/</t>
+          <t>https://www.linkedin.com/in/ktpham-1024/</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Digital Marketing &amp; Sales Strategy Intern</t>
+          <t>Channel Marketing Specialist</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
@@ -14141,12 +14141,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Kenny Pham</t>
+          <t>Brian Chou</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Alpha Beta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -14157,22 +14157,22 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>NZXT, Inc.</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ktpham-1024/</t>
+          <t>https://www.linkedin.com/in/brianchou121/</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Channel Marketing Specialist</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
@@ -14185,12 +14185,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Brian Chou</t>
+          <t>Brian Anderson</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -14201,22 +14201,22 @@
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Desmarais LLP</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/brianchou121/</t>
+          <t>https://www.linkedin.com/in/brian-l-anderson/</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
@@ -14229,12 +14229,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Brian Anderson</t>
+          <t>Madeline Li</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -14245,22 +14245,22 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Desmarais LLP</t>
+          <t>Thriveworks</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/brian-l-anderson/</t>
+          <t>https://www.linkedin.com/in/maddieli/</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Marketing Associate</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
@@ -14273,12 +14273,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Madeline Li</t>
+          <t>Malavika Basu</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Alpha Gamma</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -14289,22 +14289,22 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Thriveworks</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/maddieli/</t>
+          <t>https://www.linkedin.com/in/malavikabasu/</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Marketing Associate</t>
+          <t>Corporate Banking Associate</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -14317,12 +14317,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Malavika Basu</t>
+          <t>Megha Bhargava</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Alpha Gamma</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/malavikabasu/</t>
+          <t>https://www.linkedin.com/in/megha-bhargava/</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Corporate Banking Associate</t>
+          <t>Sales Strategy and Operations Associate</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
@@ -14361,12 +14361,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Megha Bhargava</t>
+          <t>Winnie Qi</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Mu</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -14377,22 +14377,22 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/megha-bhargava/</t>
+          <t>https://www.linkedin.com/in/winnie-qi21/</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Sales Strategy and Operations Associate</t>
+          <t>Financial Analyst, WW Sales Finance - iPad Strategy</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
@@ -14405,12 +14405,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Winnie Qi</t>
+          <t>Haley Truong</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Alpha Mu</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -14421,22 +14421,22 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>HCVT</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/winnie-qi21/</t>
+          <t>https://www.linkedin.com/in/haley-truong/</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Financial Analyst, WW Sales Finance - iPad Strategy</t>
+          <t>Advanced Tax Staff Accountant</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
@@ -14449,38 +14449,38 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Haley Truong</t>
+          <t>Albert Hoang</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Chi</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Su-Hung-Green</t>
+          <t>Wang-Zhu</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>HCVT</t>
+          <t>Crusoe</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/haley-truong/</t>
+          <t>https://www.linkedin.com/in/albert-hoang/</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Advanced Tax Staff Accountant</t>
+          <t>Legal Engineer</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -14493,12 +14493,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Albert Hoang</t>
+          <t>Sharon Phan</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>Omega</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -14509,22 +14509,22 @@
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Crusoe</t>
+          <t>Recruitics</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/albert-hoang/</t>
+          <t>https://www.linkedin.com/in/phansharon/</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Legal Engineer</t>
+          <t>Performance Marketing Manager</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -14537,12 +14537,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Sharon Phan</t>
+          <t>Steven Wang</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Omega</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -14553,22 +14553,22 @@
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Recruitics</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/phansharon/</t>
+          <t>https://www.linkedin.com/in/steven-hin-wang/</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Performance Marketing Manager</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
@@ -14581,12 +14581,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Steven Wang</t>
+          <t>Julia Vuong</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -14597,22 +14597,22 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/steven-hin-wang/</t>
+          <t>https://www.linkedin.com/in/vuongjulia/</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Technology Risk Consultant</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
@@ -14625,12 +14625,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Julia Vuong</t>
+          <t>Crystal Ly</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Zeta</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -14641,22 +14641,22 @@
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vuongjulia/</t>
+          <t>https://www.linkedin.com/in/crystal-ly/</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Senior Technology Risk Consultant</t>
+          <t>Lifecycle Marketing Specialist</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
@@ -14669,12 +14669,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Crystal Ly</t>
+          <t>Meghan Cadigal</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Alpha Zeta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -14685,22 +14685,22 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Client Services</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/crystal-ly/</t>
+          <t>https://www.linkedin.com/in/meghan-cadigal/</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Lifecycle Marketing Specialist</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -14713,12 +14713,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Meghan Cadigal</t>
+          <t>David Ayala</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -14729,22 +14729,22 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Client Services</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>NetSuite</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/meghan-cadigal/</t>
+          <t>https://www.linkedin.com/in/davidayala1/</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Account Executive</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -14757,12 +14757,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>David Ayala</t>
+          <t>Ting Ting Huang</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14773,22 +14773,22 @@
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>NetSuite</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/davidayala1/</t>
+          <t>https://www.linkedin.com/in/tingthuang/</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Account Executive</t>
+          <t>Technical Program Manager II</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
@@ -14801,12 +14801,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ting Ting Huang</t>
+          <t>Dylan Tanzil</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14817,22 +14817,22 @@
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Project Management</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t xml:space="preserve">L.S. CONGLETON &amp; ASSOCIATES </t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tingthuang/</t>
+          <t>https://www.linkedin.com/in/dylantanzil/</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Technical Program Manager II</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
@@ -14845,12 +14845,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Dylan Tanzil</t>
+          <t>Ai Toyama</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Xi</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14866,17 +14866,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">L.S. CONGLETON &amp; ASSOCIATES </t>
+          <t xml:space="preserve">STEREOSCOPE COFFEE </t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/dylantanzil/</t>
+          <t>https://www.linkedin.com/in/ai-toyama/</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -14889,12 +14889,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ai Toyama</t>
+          <t>Ryan Lau</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Alpha Xi</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14905,22 +14905,22 @@
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">STEREOSCOPE COFFEE </t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ai-toyama/</t>
+          <t>https://www.linkedin.com/in/ryanclau/</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -14933,12 +14933,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Ryan Lau</t>
+          <t>Aarti Vellimedu</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Kappa</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14954,17 +14954,17 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ryanclau/</t>
+          <t>https://www.linkedin.com/in/aartivellimedu/</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Senior Associate Consultant</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
@@ -14977,12 +14977,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Aarti Vellimedu</t>
+          <t>Aryan Bajaria</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Alpha Kappa</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14993,22 +14993,22 @@
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Asset and Wealth Management</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>J.P. Morgan</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aartivellimedu/</t>
+          <t>https://www.linkedin.com/in/aryanbajaria/</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Senior Associate Consultant</t>
+          <t>AWM Analyst</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -15021,38 +15021,38 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Aryan Bajaria</t>
+          <t>Alan Lim</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Wang-Zhu</t>
+          <t>Wong-Li</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Asset and Wealth Management</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>J.P. Morgan</t>
+          <t>Western Alliance Bank</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aryanbajaria/</t>
+          <t>https://www.linkedin.com/in/alanedwardlim/</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>AWM Analyst</t>
+          <t>Senior Credit Analyst</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
@@ -15065,12 +15065,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Alan Lim</t>
+          <t>Emily Su</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Theta</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -15086,17 +15086,17 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Western Alliance Bank</t>
+          <t>Dolby Laboratories</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alanedwardlim/</t>
+          <t>https://www.linkedin.com/in/emilysu830/</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Senior Credit Analyst</t>
+          <t>IT Business Systems Analyst Intern</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -15109,12 +15109,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Emily Su</t>
+          <t>Tommy Truong</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Alpha Theta</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -15130,17 +15130,17 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dolby Laboratories</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/emilysu830/</t>
+          <t>https://www.linkedin.com/in/tommytruong482/</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>IT Business Systems Analyst Intern</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -15153,12 +15153,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Tommy Truong</t>
+          <t>Evelyn Wu</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -15169,24 +15169,16 @@
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/tommytruong482/</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/in/evelynaw/</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
@@ -15197,32 +15189,40 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Evelyn Wu</t>
+          <t>Krystal Cheung</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Alpha Nu</t>
+          <t>Psi</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Wong-Li</t>
+          <t>Zhang-Feng</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Northwestern Mutual</t>
+        </is>
+      </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/evelynaw/</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr"/>
+          <t>https://www.linkedin.com/in/krycheung/</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
@@ -15233,12 +15233,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Krystal Cheung</t>
+          <t>Alex Tran</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Psi</t>
+          <t>Alpha Beta</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -15249,22 +15249,22 @@
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>The Pokémon Company International</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/krycheung/</t>
+          <t>https://www.linkedin.com/in/alexlawtran/</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
@@ -15277,12 +15277,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Alex Tran</t>
+          <t>Edward Li</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Alpha Beta</t>
+          <t>Alpha Epsilon</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15298,17 +15298,17 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>The Pokémon Company International</t>
+          <t>Crosby</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/alexlawtran/</t>
+          <t>https://www.linkedin.com/in/edwardhanli/</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -15321,12 +15321,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Edward Li</t>
+          <t>Lisa Deng</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Alpha Epsilon</t>
+          <t>Alpha Eta</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -15342,17 +15342,17 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Crosby</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/edwardhanli/</t>
+          <t>https://www.linkedin.com/in/lisadeng1/</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>Senior Account Executive</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -15365,12 +15365,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Lisa Deng</t>
+          <t>Aayush Shah</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Alpha Eta</t>
+          <t>Alpha Iota</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -15381,22 +15381,22 @@
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lisadeng1/</t>
+          <t>https://www.linkedin.com/in/aayushrshah/</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Associate Consultant</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -15409,12 +15409,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Aayush Shah</t>
+          <t>Amanda Nguyen</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Alpha Iota</t>
+          <t>Alpha Lambda</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -15425,22 +15425,22 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aayushrshah/</t>
+          <t>https://www.linkedin.com/in/attn/</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Associate Consultant</t>
+          <t>Product Marketing Manager, Copilot</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
@@ -15453,12 +15453,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Amanda Nguyen</t>
+          <t>Jorina Chen</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alpha Lambda</t>
+          <t>Alpha Nu</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -15469,22 +15469,22 @@
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/attn/</t>
+          <t>https://www.linkedin.com/in/jorinachen/</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, Copilot</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
@@ -15494,50 +15494,6 @@
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr"/>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Jorina Chen</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Alpha Nu</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Zhang-Feng</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Atlassian</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jorinachen/</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>Product Designer</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
-      <c r="L341" t="inlineStr"/>
-      <c r="M341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/alumni-data.xlsx
+++ b/public/alumni-data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +527,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -545,12 +545,6 @@
           <t>Network Marketing Collaborator</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,12 +587,6 @@
           <t>Business Program Manager</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -616,10 +604,9 @@
           <t>Chang-Dang</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -637,12 +624,6 @@
           <t>Senior Manager, North America Consulting</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,7 +648,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -685,12 +666,6 @@
           <t>Senior Accountant</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -733,16 +708,12 @@
           <t>Sr. Director, Analytics</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>LAST UPDATED</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="3" t="n">
         <v>45698</v>
       </c>
     </row>
@@ -762,21 +733,11 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -801,7 +762,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -819,12 +780,6 @@
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -849,7 +804,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sustainability</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -867,12 +822,6 @@
           <t xml:space="preserve">Renewable Natural Gas (RNG) Senior Advisor - Sustainability </t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -897,7 +846,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Product Management</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -915,12 +864,6 @@
           <t>Delivery Lead</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -945,7 +888,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -953,14 +896,6 @@
           <t>Alliance Apparel</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1003,12 +938,6 @@
           <t>Legal Intern</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1033,7 +962,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Media/Entertainment</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1041,14 +970,6 @@
           <t>StyleHaul</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1073,7 +994,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1091,12 +1012,6 @@
           <t>Conversion Rate Optimization Manager, Web</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1139,12 +1054,6 @@
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1187,12 +1096,6 @@
           <t>International Tax Senior Manager</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1217,7 +1120,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Food &amp; Beverage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1225,14 +1128,6 @@
           <t>Danone NA</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1257,7 +1152,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1265,14 +1160,6 @@
           <t>Tipalti</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1315,12 +1202,6 @@
           <t>Vice President, Digital Product &amp; Design</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1345,7 +1226,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1353,14 +1234,6 @@
           <t>Sony</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1403,12 +1276,6 @@
           <t>Principal Consultant</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1451,12 +1318,6 @@
           <t>Senior Financial Analyst at Google Cloud</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1499,12 +1360,6 @@
           <t>Senior Staff Product Designer</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1547,12 +1402,6 @@
           <t>UX Designer</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1595,12 +1444,6 @@
           <t>Broker Associate</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1625,7 +1468,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1643,12 +1486,6 @@
           <t>Compliance Officer</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1691,12 +1528,6 @@
           <t>Financial Analysis, Advisor</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1739,12 +1570,6 @@
           <t>Head of Global Customer Experience Strategy</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1769,7 +1594,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1777,14 +1602,6 @@
           <t>Olo</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1827,12 +1644,6 @@
           <t>Vice President, Institutional Advisory Services</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1875,12 +1686,6 @@
           <t>Global Product Manager</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1923,12 +1728,6 @@
           <t>GTM Operations Lead - North America, Revenue Operations</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1953,7 +1752,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1971,12 +1770,6 @@
           <t>Realtor • Commercial &amp; Residential</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2004,19 +1797,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/christopher-liang-42ab6919/</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2059,12 +1844,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2089,7 +1868,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2107,12 +1886,6 @@
           <t>Head of Reporting &amp; Frameworks</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2155,12 +1928,6 @@
           <t>Drops Marketing Project Manager @ Beats</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2185,7 +1952,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Client Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2203,12 +1970,6 @@
           <t>VP of Success, Solutions and Services</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2233,7 +1994,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2251,12 +2012,6 @@
           <t>Business Economics Student</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2299,12 +2054,6 @@
           <t>Associate Director - Operations &amp; Strategic Alliances</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2329,7 +2078,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2347,12 +2096,6 @@
           <t>Lead, Product Marketing</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2377,7 +2120,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2395,12 +2138,6 @@
           <t>Salesforce Consultant</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2425,7 +2162,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2433,14 +2170,6 @@
           <t>Demand Base</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2465,7 +2194,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2473,14 +2202,6 @@
           <t>Macy's</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2505,7 +2226,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2513,14 +2234,6 @@
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2545,7 +2258,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail/E-commerce</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2553,14 +2266,6 @@
           <t>Newegg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2603,12 +2308,6 @@
           <t>Lead Product Designer</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2633,7 +2332,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2641,14 +2340,6 @@
           <t>The Event Loft</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2691,12 +2382,6 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2739,12 +2424,6 @@
           <t>VP of Mortgage Lending at Guaranteed Rate Affinity NMLS 1380693</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2769,7 +2448,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2777,14 +2456,6 @@
           <t>Equinix</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2827,12 +2498,6 @@
           <t>Human Resources Information System Analyst</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2875,12 +2540,6 @@
           <t>TA Operations Partner</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2923,12 +2582,6 @@
           <t>Business Strategy &amp; Data Analyst</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2971,12 +2624,6 @@
           <t>Audit and Assurance Intern</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3001,7 +2648,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3019,12 +2666,6 @@
           <t>Associate Key Account Manager</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3049,7 +2690,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3067,12 +2708,6 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3090,21 +2725,11 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3137,14 +2762,6 @@
           <t>Verizon Digital Media</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3169,7 +2786,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Food &amp; Beverage</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3177,14 +2794,6 @@
           <t>Popeyes</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3202,21 +2811,11 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3241,7 +2840,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3249,14 +2848,6 @@
           <t>Chanje</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3281,7 +2872,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3299,12 +2890,6 @@
           <t>Research Recruiter</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3347,12 +2932,6 @@
           <t>Internal Controls Manager</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3377,7 +2956,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3385,14 +2964,6 @@
           <t>eHealth</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3417,7 +2988,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3435,12 +3006,6 @@
           <t>Data &amp; Business Analyst</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3465,7 +3030,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3473,14 +3038,6 @@
           <t>Protiviti</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3505,7 +3062,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3523,12 +3080,6 @@
           <t>Director, Client Solutions</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3571,12 +3122,6 @@
           <t>Strategic Finance Manager | GTM Growth &amp; Performance</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3601,7 +3146,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3619,12 +3164,6 @@
           <t>Principal Solutions Consultant &amp; Team Lead</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3667,12 +3206,6 @@
           <t>Lead Program Manager, Talent Operations</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3697,7 +3230,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3705,14 +3238,6 @@
           <t>Lyft</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3737,7 +3262,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3745,14 +3270,6 @@
           <t>Prologis</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3795,12 +3312,6 @@
           <t>Sr. Manager, Paid Media Marketing</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3843,12 +3354,6 @@
           <t>Sales Engineer</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3873,7 +3378,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3891,12 +3396,6 @@
           <t>Product Analyst</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3921,7 +3420,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3929,14 +3428,6 @@
           <t>Dept of Homeland Security</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3961,7 +3452,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3969,14 +3460,6 @@
           <t>213 Hospitality</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4001,7 +3484,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4009,14 +3492,6 @@
           <t>iBuyPower</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4041,7 +3516,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4049,14 +3524,6 @@
           <t>Midnight Oil</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4074,21 +3541,11 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4113,7 +3570,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4131,12 +3588,6 @@
           <t>Chief Operating Officer</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4161,7 +3612,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4169,14 +3620,6 @@
           <t>Figure Eight</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4201,7 +3644,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4209,14 +3652,6 @@
           <t>Proteus Digital Health</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4241,7 +3676,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4249,14 +3684,6 @@
           <t>PIMCO</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4299,12 +3726,6 @@
           <t>Senior Finance Manager</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4329,7 +3750,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4347,12 +3768,6 @@
           <t>Realtor</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4395,12 +3810,6 @@
           <t>Staff Design Manager</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4425,7 +3834,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4443,12 +3852,6 @@
           <t>Technical Platform Owner, Loyalty</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4473,7 +3876,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4491,12 +3894,6 @@
           <t>Assistant Director of Budget and Planning Systems</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4514,21 +3911,11 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4553,7 +3940,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4571,12 +3958,6 @@
           <t>Sr. Sales Operations Manager</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4619,12 +4000,6 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4657,14 +4032,6 @@
           <t>LayerCake Marketing</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4689,7 +4056,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4707,12 +4074,6 @@
           <t>Chief Product Officer</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4755,12 +4116,6 @@
           <t>Senior Brand Manager</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4778,21 +4133,11 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4810,10 +4155,9 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4831,12 +4175,6 @@
           <t>Internal Medicine Resident</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4861,7 +4199,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4869,14 +4207,6 @@
           <t>Amazon</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4901,7 +4231,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4919,12 +4249,6 @@
           <t>Account Executive</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4949,7 +4273,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4957,14 +4281,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4989,7 +4305,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Media/Entertainment</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4997,14 +4313,6 @@
           <t>Activision Blizzard</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5037,14 +4345,6 @@
           <t>SES Insurance Brokerage</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5062,21 +4362,11 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5119,12 +4409,6 @@
           <t xml:space="preserve">Program Manager, Strategy and Operations (AI Automation) </t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5149,7 +4433,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Media/Entertainment</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5167,12 +4451,6 @@
           <t>Senior Account Manager</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5197,7 +4475,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5215,12 +4493,6 @@
           <t>Business Solutions Manager</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5263,12 +4535,6 @@
           <t>Manager</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5293,7 +4559,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5301,14 +4567,6 @@
           <t>Top Guy Intl</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5336,15 +4594,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5369,7 +4618,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5377,14 +4626,6 @@
           <t>Connexity</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5409,7 +4650,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5417,14 +4658,6 @@
           <t>PIMCO</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5467,12 +4700,6 @@
           <t>Financial Advisor</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5515,12 +4742,6 @@
           <t>Finance Manager</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5563,12 +4784,6 @@
           <t>Media Manager</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5611,12 +4826,6 @@
           <t>Investment Analyst</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5659,12 +4868,6 @@
           <t>Senior Manager, Commercial Accounting &amp; Finance</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5689,7 +4892,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5697,14 +4900,6 @@
           <t>PBFY Flexible Packaging</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5747,12 +4942,6 @@
           <t>Product Marketing Associate</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5795,12 +4984,6 @@
           <t>Product Marketing Ambassador</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5843,12 +5026,6 @@
           <t>Industrial Manufacturing Engineer</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5891,12 +5068,6 @@
           <t>Associate Product Marketing Manager Intern</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5921,7 +5092,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5939,12 +5110,6 @@
           <t>Group Manager, Partner Development</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5969,7 +5134,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5987,12 +5152,6 @@
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6035,12 +5194,6 @@
           <t>Human Resources Business Partner</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6065,7 +5218,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6083,12 +5236,6 @@
           <t>Planning Manager</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6131,12 +5278,6 @@
           <t>Director of Compliance Data Program</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6161,7 +5302,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6179,12 +5320,6 @@
           <t>Client Solutions Manager</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6212,15 +5347,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6263,12 +5389,6 @@
           <t>Acquisition Marketing Manager</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6311,12 +5431,6 @@
           <t>Chief Technology Officer</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6359,12 +5473,6 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6389,7 +5497,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6397,14 +5505,6 @@
           <t>Recurly</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6447,12 +5547,6 @@
           <t>Strategic Revenue Growth Management / Trade Strategy</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6495,12 +5589,6 @@
           <t>Attorney</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6543,12 +5631,6 @@
           <t>Senior Manager, Compliance and Controls</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6591,12 +5673,6 @@
           <t>Director, Strategic Planning</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6624,15 +5700,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6657,7 +5724,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6665,14 +5732,6 @@
           <t>EY</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6697,7 +5756,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6705,14 +5764,6 @@
           <t>BDO</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6755,12 +5806,6 @@
           <t>Head of Outbound Product Management, Legal &amp; Contract Operations</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6785,7 +5830,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6803,12 +5848,6 @@
           <t>Associate Director</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6833,7 +5872,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Media/Entertainment</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6846,13 +5885,6 @@
           <t>https://www.linkedin.com/school/university-of-california-irvine/people/?keywords=Ran%20Cao</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6895,12 +5927,6 @@
           <t>Lead Sr. Social Media Manager</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6943,12 +5969,6 @@
           <t>Insurance Broker</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6981,14 +6001,6 @@
           <t>YLS Financial &amp; Insurance Services</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7013,7 +6025,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7031,12 +6043,6 @@
           <t>Senior Manager, Pricing and Estimating</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7054,21 +6060,11 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7093,7 +6089,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7101,14 +6097,6 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7151,12 +6139,6 @@
           <t>Sr. Product Designer</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7199,12 +6181,6 @@
           <t>Senior Manager - Performance &amp; Digital Marketing</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7229,7 +6205,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7237,14 +6213,6 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7287,12 +6255,6 @@
           <t>Founder | Exclusive U.S. Distributor of Lamborghini Wine</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7317,7 +6279,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7335,12 +6297,6 @@
           <t>Technical SEO Specialist</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7365,7 +6321,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7373,14 +6329,6 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7423,12 +6371,6 @@
           <t>Sr. Product Marketing Manager, Fraud and Add-ons</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7471,12 +6413,6 @@
           <t>Manager, Technical Accounting and SEC Reporting</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7519,12 +6455,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7567,12 +6497,6 @@
           <t>Software Development Engineer II - Regulatory, Intelligence, Safety, &amp; Compliance</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7615,12 +6539,6 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7663,12 +6581,6 @@
           <t>Analyst</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7693,7 +6605,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7711,12 +6623,6 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7759,12 +6665,6 @@
           <t>Private</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7807,12 +6707,6 @@
           <t>Senior Project Manager/Scrum Master</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7830,21 +6724,11 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7872,19 +6756,11 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/isaac-lau-b6419212/</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7909,7 +6785,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7917,14 +6793,6 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7952,15 +6820,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8003,12 +6862,6 @@
           <t>Head of Growth</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8051,12 +6904,6 @@
           <t>Staff Product Manager</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8081,7 +6928,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8099,12 +6946,6 @@
           <t>Compliance Specialist</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8129,7 +6970,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8147,12 +6988,6 @@
           <t>FPP Revenue Agent</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8195,12 +7030,6 @@
           <t>Monetization Strategy Specialist</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8228,15 +7057,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8261,7 +7081,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8269,14 +7089,6 @@
           <t>Capital One</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8319,12 +7131,6 @@
           <t>Sr. Associate, Campaign Operations</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8367,12 +7173,6 @@
           <t>Business Development &amp; Strategic Non-dilutive Funding</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8397,7 +7197,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8405,14 +7205,6 @@
           <t>CBRE / USC Marshall 2020</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8437,7 +7229,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8445,14 +7237,6 @@
           <t>Samsung Semiconductors</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8495,12 +7279,6 @@
           <t>Software Engineer III</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8543,12 +7321,6 @@
           <t>Lead Data Scientist</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8591,12 +7363,6 @@
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8639,12 +7405,6 @@
           <t>Senior FP&amp;A Analyst</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8687,12 +7447,6 @@
           <t>Business Manager</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8735,12 +7489,6 @@
           <t>Ecommerce Specialist</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8783,12 +7531,6 @@
           <t>Tech Implementation and Integrations, Program Manager II</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8821,14 +7563,6 @@
           <t>Self-Employed</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8853,7 +7587,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8861,14 +7595,6 @@
           <t>Workplace by Facebook</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8911,12 +7637,6 @@
           <t>Senior Product Marketing Manager, Monopoly GO!</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8934,10 +7654,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Food &amp; Beverage</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8955,12 +7674,6 @@
           <t>Administrative Assistant</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8985,7 +7698,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8993,14 +7706,6 @@
           <t>Booz Allen Hamilton</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9025,7 +7730,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9033,14 +7738,6 @@
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9065,7 +7762,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9073,14 +7770,6 @@
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9123,12 +7812,6 @@
           <t>Senior Tax Manager</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9156,15 +7839,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9189,7 +7863,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9207,12 +7881,6 @@
           <t>Wealth Management Advisor</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9237,7 +7905,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9255,12 +7923,6 @@
           <t>Assistant Director of Foundation Center</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9303,12 +7965,6 @@
           <t>Senior Accountant</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9351,12 +8007,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9399,12 +8049,6 @@
           <t>Director, Strategic Finance</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9429,7 +8073,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9437,14 +8081,6 @@
           <t>Apple</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9469,7 +8105,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9477,14 +8113,6 @@
           <t>PwC</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9502,21 +8130,11 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9541,7 +8159,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9559,12 +8177,6 @@
           <t>Senior Manager</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9607,12 +8219,6 @@
           <t>Senior Technical Program Manager</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9655,12 +8261,6 @@
           <t>Product Marketing, Guest</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9685,7 +8285,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Media/Entertainment</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9703,12 +8303,6 @@
           <t>Analyst</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9733,7 +8327,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9741,14 +8335,6 @@
           <t>Stanford</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9773,7 +8359,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entrepreneurship</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9791,12 +8377,6 @@
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9821,7 +8401,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9839,12 +8419,6 @@
           <t>Office Manager</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9887,12 +8461,6 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9917,7 +8485,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9935,12 +8503,6 @@
           <t>Results Manager</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9965,7 +8527,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9973,14 +8535,6 @@
           <t>EY</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9998,21 +8552,11 @@
           <t>Wong-Li</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10055,12 +8599,6 @@
           <t>Account Strategist</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10088,15 +8626,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10124,15 +8653,6 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10157,7 +8677,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -10165,14 +8685,6 @@
           <t>PWC</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10197,7 +8709,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10205,14 +8717,6 @@
           <t>Redbubble</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10237,7 +8741,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10245,14 +8749,6 @@
           <t>AirBnb</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10277,7 +8773,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -10295,12 +8791,6 @@
           <t>Vice President - Delta One Trading</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10343,12 +8833,6 @@
           <t>Lead Product Manager</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10373,7 +8857,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10391,12 +8875,6 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10421,7 +8899,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10439,12 +8917,6 @@
           <t>Operations &amp; Data Analyst</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10469,7 +8941,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10477,14 +8949,6 @@
           <t>CA Dept Business Oversight</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -10502,21 +8966,11 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10541,7 +8995,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10559,12 +9013,6 @@
           <t>Senior Director, Human Resources</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10589,7 +9037,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10607,12 +9055,6 @@
           <t>Senior Manager, Regional Controller</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10637,7 +9079,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -10655,12 +9097,6 @@
           <t>Account Director</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10703,12 +9139,6 @@
           <t>Career Break</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10733,7 +9163,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -10741,14 +9171,6 @@
           <t>Visa</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10791,12 +9213,6 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10821,7 +9237,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -10839,12 +9255,6 @@
           <t>Business Career Foundation Program | Contracts &amp; Pricing</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10869,7 +9279,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -10877,14 +9287,6 @@
           <t>FaceBook</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10927,12 +9329,6 @@
           <t>Co-Founder</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10975,12 +9371,6 @@
           <t>Technical Product Manager (TDP)</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11023,12 +9413,6 @@
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11046,7 +9430,6 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -11067,12 +9450,6 @@
           <t>Customer Engineer</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11090,7 +9467,6 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -11111,12 +9487,6 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11134,10 +9504,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11155,12 +9524,6 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11178,10 +9541,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -11199,12 +9561,6 @@
           <t>PHD Student</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11222,7 +9578,6 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -11243,12 +9598,6 @@
           <t>Marketing Manager</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11266,7 +9615,6 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -11287,12 +9635,6 @@
           <t>Transformation Strategy Manager</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11310,10 +9652,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11331,12 +9672,6 @@
           <t>Co-Brand Strategic Partnerships Analyst</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11354,10 +9689,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11375,12 +9709,6 @@
           <t>Consultant</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11398,7 +9726,6 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -11419,12 +9746,6 @@
           <t>Associate Product Marketing Manager</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11442,10 +9763,9 @@
           <t>Lough-Yu</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -11463,12 +9783,6 @@
           <t>Director of Operations</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -11486,25 +9800,16 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alecwong44/</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -11522,7 +9827,6 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>UI/UX</t>
@@ -11543,12 +9847,6 @@
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -11566,10 +9864,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -11587,12 +9884,6 @@
           <t>Product Marketer</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -11610,10 +9901,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Government</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -11631,12 +9921,6 @@
           <t>Delegate</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -11654,7 +9938,6 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>Strategy</t>
@@ -11675,12 +9958,6 @@
           <t>Manager, Customer Success</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11698,10 +9975,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -11719,12 +9995,6 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11742,7 +10012,6 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>Media/Entertainment</t>
@@ -11763,12 +10032,6 @@
           <t>Senior Social Media Associate</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11786,10 +10049,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -11807,12 +10069,6 @@
           <t>Client Solutions Manager</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11830,7 +10086,6 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>HR</t>
@@ -11851,12 +10106,6 @@
           <t>Compensation Analyst</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11874,10 +10123,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -11895,12 +10143,6 @@
           <t>Splunk Platform Partner Go-To-Market Manager</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11918,10 +10160,9 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -11939,12 +10180,6 @@
           <t>Guest Experiences Lead</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11962,7 +10197,6 @@
           <t>Chang-McGrath</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
           <t>Project Management</t>
@@ -11983,12 +10217,6 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12006,21 +10234,11 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12038,7 +10256,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>Strategy</t>
@@ -12059,12 +10276,6 @@
           <t>Strategic Partnerships Manager</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12082,7 +10293,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -12103,12 +10313,6 @@
           <t>Strategic Finance &amp; Analytics</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12126,7 +10330,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>Data</t>
@@ -12147,12 +10350,6 @@
           <t>Workforce Analyst</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12170,7 +10367,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>Data</t>
@@ -12191,12 +10387,6 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12214,7 +10404,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12235,12 +10424,6 @@
           <t>Software Development Engineer II</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12258,7 +10441,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12279,12 +10461,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12302,7 +10478,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12323,12 +10498,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -12346,7 +10515,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -12367,12 +10535,6 @@
           <t>Strategy &amp; Analytics Lead</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -12390,7 +10552,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
           <t>Data</t>
@@ -12411,12 +10572,6 @@
           <t>Business Analyst 2</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -12434,7 +10589,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -12455,12 +10609,6 @@
           <t>Marketing Manager</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -12478,25 +10626,16 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jinfukusumi/</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -12514,7 +10653,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -12535,12 +10673,6 @@
           <t>CSG - Strategy &amp; Analytics Senior Analyst</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -12558,21 +10690,11 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -12590,7 +10712,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12611,12 +10732,6 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -12634,7 +10749,6 @@
           <t>Chen-Ho</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -12655,12 +10769,6 @@
           <t>Corporate Strategy &amp; Development - Strategic Partnerships</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12678,7 +10786,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12699,12 +10806,6 @@
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12722,7 +10823,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12743,12 +10843,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12766,7 +10860,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -12787,12 +10880,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12810,10 +10897,9 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -12831,12 +10917,6 @@
           <t>Clinical Nurse II</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12854,7 +10934,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
           <t>Accounting</t>
@@ -12875,12 +10954,6 @@
           <t>Accounting Manager</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12898,7 +10971,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -12919,12 +10991,6 @@
           <t>Account-Based Marketing Specialist</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12942,7 +11008,6 @@
           <t>Chew-Mark</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -12963,12 +11028,6 @@
           <t>Business Analyst</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12986,7 +11045,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -13007,12 +11065,6 @@
           <t>Senior Analyst, Development Finance</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13030,7 +11082,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -13051,12 +11102,6 @@
           <t>Corporate Finance &amp; Strategy Senior Associate</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13074,7 +11119,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -13095,12 +11139,6 @@
           <t>Associate Manager, Monetization Strategy</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13118,7 +11156,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>Product Management</t>
@@ -13139,12 +11176,6 @@
           <t>Product Manager</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13162,7 +11193,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -13183,12 +11213,6 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13206,7 +11230,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -13227,12 +11250,6 @@
           <t>Investor Relations Associate</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -13250,7 +11267,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>Data</t>
@@ -13271,12 +11287,6 @@
           <t>Senior Data Analyst</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -13294,10 +11304,9 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -13315,12 +11324,6 @@
           <t>Global Benefits Analyst</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -13338,7 +11341,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -13359,12 +11361,6 @@
           <t>Flight Software Engineer</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -13382,21 +11378,11 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -13414,7 +11400,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -13435,12 +11420,6 @@
           <t>Builder</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -13458,10 +11437,9 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -13479,12 +11457,6 @@
           <t>UX E-Commerce Manager</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -13502,7 +11474,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -13523,12 +11494,6 @@
           <t>Product Marketing Manager</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -13546,7 +11511,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -13567,12 +11531,6 @@
           <t>Growth Marketing Manager</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -13590,7 +11548,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -13611,12 +11568,6 @@
           <t>Financial Analyst</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -13634,7 +11585,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>Project Management</t>
@@ -13655,12 +11605,6 @@
           <t>Senior Project Manager</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -13678,10 +11622,9 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -13699,12 +11642,6 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13722,7 +11659,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -13743,12 +11679,6 @@
           <t>Financial Analyst, LimFlow BU</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13766,25 +11696,16 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/markmembrebe1/</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13802,7 +11723,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>Product Management</t>
@@ -13823,12 +11743,6 @@
           <t xml:space="preserve">Product Manager, Personalization </t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13846,7 +11760,6 @@
           <t>Huang-Merchant</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>Data</t>
@@ -13867,12 +11780,6 @@
           <t>Data Scientist, Full Stack</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13890,10 +11797,9 @@
           <t>Liang-Lin</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -13911,12 +11817,6 @@
           <t>Sr. Investment Performance Analyst</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13934,7 +11834,6 @@
           <t>Liang-Lin</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -13955,12 +11854,6 @@
           <t>Founder in Residence</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13978,10 +11871,9 @@
           <t>Liang-Lin</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -13999,12 +11891,6 @@
           <t>Campaign Manager</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
-      <c r="M306" t="inlineStr"/>
-      <c r="N306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14022,7 +11908,6 @@
           <t>Liang-Lin</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>HR</t>
@@ -14043,12 +11928,6 @@
           <t>Emerging Talent Program Manager</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14066,7 +11945,6 @@
           <t>Liang-Lin</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -14087,12 +11965,6 @@
           <t>Digital Marketing &amp; Sales Strategy Intern</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14110,7 +11982,6 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -14131,12 +12002,6 @@
           <t>Channel Marketing Specialist</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -14154,7 +12019,6 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14175,12 +12039,6 @@
           <t>Software Development Engineer II</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -14198,10 +12056,9 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -14219,12 +12076,6 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -14242,7 +12093,6 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -14263,12 +12113,6 @@
           <t>Marketing Associate</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -14286,10 +12130,9 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -14307,12 +12150,6 @@
           <t>Corporate Banking Associate</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -14330,10 +12167,9 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -14351,12 +12187,6 @@
           <t>Sales Strategy and Operations Associate</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -14374,7 +12204,6 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>Finance</t>
@@ -14395,12 +12224,6 @@
           <t>Financial Analyst, WW Sales Finance - iPad Strategy</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -14418,7 +12241,6 @@
           <t>Su-Hung-Green</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>Accounting</t>
@@ -14439,12 +12261,6 @@
           <t>Advanced Tax Staff Accountant</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -14462,10 +12278,9 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -14483,12 +12298,6 @@
           <t>Legal Engineer</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -14506,7 +12315,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -14527,12 +12335,6 @@
           <t>Performance Marketing Manager</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -14550,7 +12352,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14571,12 +12372,6 @@
           <t>Software Development Engineer II</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -14594,7 +12389,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -14615,12 +12409,6 @@
           <t>Senior Technology Risk Consultant</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
-      <c r="N320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -14638,7 +12426,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -14659,12 +12446,6 @@
           <t>Lifecycle Marketing Specialist</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -14682,7 +12463,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>Client Services</t>
@@ -14703,12 +12483,6 @@
           <t>Customer Success Manager</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -14726,10 +12500,9 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -14747,12 +12520,6 @@
           <t>Account Executive</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14770,7 +12537,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>Project Management</t>
@@ -14791,12 +12557,6 @@
           <t>Technical Program Manager II</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14814,10 +12574,9 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -14835,12 +12594,6 @@
           <t>Intern</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14858,10 +12611,9 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Food &amp; Beverage</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -14879,12 +12631,6 @@
           <t>Manager</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14902,7 +12648,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -14923,12 +12668,6 @@
           <t>Consultant</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14946,7 +12685,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>Consulting</t>
@@ -14967,12 +12705,6 @@
           <t>Senior Associate Consultant</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -14990,7 +12722,6 @@
           <t>Wang-Zhu</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>Asset and Wealth Management</t>
@@ -15011,12 +12742,6 @@
           <t>AWM Analyst</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15034,10 +12759,9 @@
           <t>Wong-Li</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -15055,12 +12779,6 @@
           <t>Senior Credit Analyst</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -15078,7 +12796,6 @@
           <t>Wong-Li</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>Data</t>
@@ -15099,12 +12816,6 @@
           <t>IT Business Systems Analyst Intern</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -15122,7 +12833,6 @@
           <t>Wong-Li</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>Data</t>
@@ -15143,12 +12853,6 @@
           <t>Analyst</t>
         </is>
       </c>
-      <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
-      <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -15166,25 +12870,16 @@
           <t>Wong-Li</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/evelynaw/</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
-      <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -15202,7 +12897,6 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -15223,12 +12917,6 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -15246,10 +12934,9 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -15267,12 +12954,6 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -15290,10 +12971,9 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -15311,12 +12991,6 @@
           <t>GTM</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -15334,10 +13008,9 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -15355,12 +13028,6 @@
           <t>Senior Account Executive</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -15378,7 +13045,6 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>Operations</t>
@@ -15399,12 +13065,6 @@
           <t>Associate Consultant</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -15422,7 +13082,6 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>Marketing</t>
@@ -15443,12 +13102,6 @@
           <t>Product Marketing Manager, Copilot</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -15466,7 +13119,6 @@
           <t>Zhang-Feng</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>UI/UX</t>
@@ -15487,12 +13139,6 @@
           <t>Product Designer</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
